--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,58 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112128595</v>
+        <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>92732</v>
+        <v>96618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2014</v>
+        <v>1080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öarna, Öarna, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353910</v>
+        <v>353955</v>
       </c>
       <c r="R2" t="n">
-        <v>6331920</v>
+        <v>6331902</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Verifierad av Anders Dahlberg</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,53 +771,1424 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead wood # Quercus robur</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lena Gustafsson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lena Gustafsson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136192425</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136192041</v>
+      </c>
+      <c r="B3" t="n">
+        <v>77839</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>353974</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6331884</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192041</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136192274</v>
+      </c>
+      <c r="B4" t="n">
+        <v>77839</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>353955</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6331902</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192274</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112128595</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92732</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öarna, Öarna, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>353910</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6331920</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Verifierad av Anders Dahlberg</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead wood # Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lena Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lena Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/112128595</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136191414</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96608</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>354027</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6331868</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191414</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136192184</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96597</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>353955</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6331902</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192184</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136191740</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96402</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>353994</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6331870</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191740</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136192452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96402</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>353955</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6331902</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192452</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136192201</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83414</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>353955</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6331902</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192201</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136191497</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>353994</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6331870</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191497</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136192690</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98148</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>354051</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6331948</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192690</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136191869</v>
+      </c>
+      <c r="B13" t="n">
+        <v>81107</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>353974</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6331884</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191869</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136192731</v>
+      </c>
+      <c r="B14" t="n">
+        <v>81107</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>354051</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6331948</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192731</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96402</v>
+        <v>96403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96402</v>
+        <v>96403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98148</v>
+        <v>98149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77839</v>
+        <v>77840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77839</v>
+        <v>77840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96609</v>
+        <v>96610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96403</v>
+        <v>96404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96403</v>
+        <v>96404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83414</v>
+        <v>83415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98149</v>
+        <v>98150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81107</v>
+        <v>81108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81107</v>
+        <v>81108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77840</v>
+        <v>77844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77840</v>
+        <v>77844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96610</v>
+        <v>96616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83415</v>
+        <v>83419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98150</v>
+        <v>98156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81108</v>
+        <v>81112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81108</v>
+        <v>81112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96626</v>
+        <v>96627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77844</v>
+        <v>77845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77844</v>
+        <v>77845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96410</v>
+        <v>96411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96410</v>
+        <v>96411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83419</v>
+        <v>83420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79705</v>
+        <v>79706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81112</v>
+        <v>81113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81112</v>
+        <v>81113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96627</v>
+        <v>96638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77845</v>
+        <v>77849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77845</v>
+        <v>77849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96617</v>
+        <v>96628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96411</v>
+        <v>96422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96411</v>
+        <v>96422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83420</v>
+        <v>83424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98157</v>
+        <v>98168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81113</v>
+        <v>81117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81113</v>
+        <v>81117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96638</v>
+        <v>96651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77849</v>
+        <v>77855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77849</v>
+        <v>77855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96628</v>
+        <v>96641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96422</v>
+        <v>96435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96422</v>
+        <v>96435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83424</v>
+        <v>83430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79710</v>
+        <v>79716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98168</v>
+        <v>98181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81117</v>
+        <v>81123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81117</v>
+        <v>81123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96651</v>
+        <v>96652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98181</v>
+        <v>98182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96652</v>
+        <v>96665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77855</v>
+        <v>77868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77855</v>
+        <v>77868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83430</v>
+        <v>83443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79716</v>
+        <v>79729</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81123</v>
+        <v>81136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81123</v>
+        <v>81136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96665</v>
+        <v>96666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77868</v>
+        <v>77869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77868</v>
+        <v>77869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83443</v>
+        <v>83444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79729</v>
+        <v>79730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81136</v>
+        <v>81137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81136</v>
+        <v>81137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
